--- a/Employee_Reports_wi48/Jayson Ruz Oligan Q0548.xlsx
+++ b/Employee_Reports_wi48/Jayson Ruz Oligan Q0548.xlsx
@@ -569,11 +569,11 @@
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -618,11 +618,11 @@
         </is>
       </c>
       <c r="H4" s="3" t="n">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -667,11 +667,11 @@
         </is>
       </c>
       <c r="H5" s="3" t="n">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -716,11 +716,11 @@
         </is>
       </c>
       <c r="H6" s="3" t="n">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -765,11 +765,11 @@
         </is>
       </c>
       <c r="H7" s="3" t="n">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -814,11 +814,11 @@
         </is>
       </c>
       <c r="H8" s="3" t="n">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -863,11 +863,11 @@
         </is>
       </c>
       <c r="H9" s="3" t="n">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -900,11 +900,11 @@
         </is>
       </c>
       <c r="H10" s="3" t="n">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -949,11 +949,11 @@
         </is>
       </c>
       <c r="H11" s="3" t="n">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -998,11 +998,11 @@
         </is>
       </c>
       <c r="H12" s="3" t="n">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
@@ -1035,11 +1035,11 @@
         </is>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-328</v>
+        <v>-331</v>
       </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J13" s="4" t="inlineStr">
@@ -1072,11 +1072,11 @@
         </is>
       </c>
       <c r="H14" s="3" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
@@ -1109,11 +1109,11 @@
         </is>
       </c>
       <c r="H15" s="3" t="n">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
@@ -1385,7 +1385,7 @@
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>7639</v>
+        <v>7636</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -1414,7 +1414,7 @@
         </is>
       </c>
       <c r="E4" s="3" t="n">
-        <v>7846</v>
+        <v>7843</v>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
